--- a/DB_demo/Import Tài Khoản.xlsx
+++ b/DB_demo/Import Tài Khoản.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\cms\DB_demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E949821-7A55-4BAB-AB96-870B1966B461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37769DEC-EC98-489A-8683-0C25F2CF840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="diemdanh_HK1_N1" sheetId="1" r:id="rId1"/>
@@ -45,35 +45,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="61">
   <si>
     <t>STT</t>
   </si>
   <si>
-    <t>PHẠM THANH PHONG</t>
-  </si>
-  <si>
-    <t>NGUYỄN QUỐC THÁI</t>
-  </si>
-  <si>
-    <t>TRẦN VIỆT ANH</t>
-  </si>
-  <si>
-    <t>NGUYỄN MINH ĐỨC</t>
-  </si>
-  <si>
-    <t>NGUYỄN QUỐC DUY KHANG</t>
-  </si>
-  <si>
-    <t>NGÔ LÊ THÀNH HẢI</t>
-  </si>
-  <si>
-    <t>BÙI VĂN ANH THẾ</t>
-  </si>
-  <si>
-    <t>25TH01</t>
-  </si>
-  <si>
     <t>25TH02</t>
   </si>
   <si>
@@ -98,56 +74,167 @@
     <t>student</t>
   </si>
   <si>
-    <t>Nguyễn Hữu Quyền</t>
-  </si>
-  <si>
-    <t>nhquyen@bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>support_admin</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thu Sương</t>
-  </si>
-  <si>
-    <t>teacher</t>
-  </si>
-  <si>
-    <t>GVNHQ</t>
-  </si>
-  <si>
-    <t>GVNTTS</t>
-  </si>
-  <si>
-    <t>nttsuong@bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050001@student.bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050002@student.bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050003@student.bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050005@student.bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050006@student.bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050007@student.bdu.edu.vn</t>
-  </si>
-  <si>
-    <t>22050008@student.bdu.edu.vn</t>
+    <t>Phan Đình Luyến</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Lệ My</t>
+  </si>
+  <si>
+    <t>Phạm Đức Thuận</t>
+  </si>
+  <si>
+    <t>TrầN Lê Ngọc Khanh</t>
+  </si>
+  <si>
+    <t>Lê Quang Phúc</t>
+  </si>
+  <si>
+    <t>Trần Minh Huân</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Ngà</t>
+  </si>
+  <si>
+    <t>Trần Bảo Huy</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Duy</t>
+  </si>
+  <si>
+    <t>Lê Hải Đông</t>
+  </si>
+  <si>
+    <t>Lê Đức Tài</t>
+  </si>
+  <si>
+    <t>Nguyễn Tuấn Khanh</t>
+  </si>
+  <si>
+    <t>Nguyễn Tấn Tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặng Ngọc Phong </t>
+  </si>
+  <si>
+    <t>Nguyễn Trọng Hiếu</t>
+  </si>
+  <si>
+    <t>Nguyễn Long Thiên Thuận</t>
+  </si>
+  <si>
+    <t>Lương Nguyễn Quốc Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Huy Hoàng</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Nhật Tân</t>
+  </si>
+  <si>
+    <t>Trần Nguyễn Phi Vũ</t>
+  </si>
+  <si>
+    <t>Lê Xuân Huy</t>
+  </si>
+  <si>
+    <t>Đỗ Sơn Tùng</t>
+  </si>
+  <si>
+    <t>Nguyễn Lâm Hùng</t>
+  </si>
+  <si>
+    <t>Phạm Quốc Việt</t>
+  </si>
+  <si>
+    <t>Lê Quang Đức</t>
+  </si>
+  <si>
+    <t>Hồ Thạch Thiên</t>
+  </si>
+  <si>
+    <t>22050036@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050039@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050062@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050066@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050067@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050068@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050070@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050080@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050081@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050084@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050090@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050091@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050093@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050094@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050095@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050096@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050098@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050099@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050101@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050102@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050103@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050110@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050111@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050112@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050119@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>22050123@student.bdu.edu.vn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,13 +269,6 @@
       <charset val="163"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="163"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -196,8 +276,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,8 +304,26 @@
         <bgColor rgb="FFEEECE1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -260,24 +372,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -289,21 +388,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,46 +645,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A10" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A27" si="0">ROW()-2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="5">
-        <v>22050001</v>
+      <c r="B2" s="9">
+        <v>22050036</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="15">
+        <v>38261</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7">
-        <v>38290</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -584,23 +692,23 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B3" s="5">
-        <v>22050002</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="7">
-        <v>38314</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>16</v>
+      <c r="B3" s="10">
+        <v>22050039</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="15">
+        <v>38283</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -608,23 +716,23 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="5">
-        <v>22050003</v>
+      <c r="B4" s="9">
+        <v>22050062</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="7">
-        <v>38289</v>
-      </c>
-      <c r="E4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="15">
+        <v>38222</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -632,23 +740,23 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="5">
-        <v>22050005</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7">
-        <v>38155</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="B5" s="10">
+        <v>22050066</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="15">
+        <v>38152</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -656,23 +764,23 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="5">
-        <v>22050006</v>
+      <c r="B6" s="9">
+        <v>22050067</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="7">
-        <v>37682</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="15">
+        <v>37802</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -680,23 +788,23 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>22050007</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7">
-        <v>38247</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>16</v>
+      <c r="B7" s="10">
+        <v>22050068</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="15">
+        <v>38311</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -704,23 +812,23 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="5">
-        <v>22050008</v>
+      <c r="B8" s="9">
+        <v>22050070</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="7">
-        <v>36560</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="15">
+        <v>37264</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -728,21 +836,23 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7">
-        <v>31472</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>21</v>
+      <c r="B9" s="11">
+        <v>22050080</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="15">
+        <v>38239</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -750,45 +860,438 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9">
+        <v>22050081</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="15">
+        <v>38248</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="10">
+        <v>22050084</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="15">
+        <v>38230</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="9">
+        <v>22050090</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15">
+        <v>37988</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="10">
+        <v>22050091</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="15">
+        <v>38053</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="9">
+        <v>22050093</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="15">
+        <v>38247</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="10">
+        <v>22050094</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="15">
+        <v>38284</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="9">
+        <v>22050095</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D16" s="15">
+        <v>38088</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="10">
+        <v>22050096</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="15">
+        <v>38039</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="9">
+        <v>22050098</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="15">
+        <v>38060</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B19" s="10">
+        <v>22050099</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="15">
+        <v>38097</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="9">
+        <v>22050101</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="15">
+        <v>38073</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B21" s="10">
+        <v>22050102</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="15">
+        <v>37987</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D10" s="9">
-        <v>30840</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
+      <c r="B22" s="9">
+        <v>22050103</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="15">
+        <v>38136</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B23" s="10">
+        <v>22050110</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="15">
+        <v>37843</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="9">
+        <v>22050111</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="15">
+        <v>38094</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="10">
+        <v>22050112</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="15">
+        <v>38174</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>19</v>
+      <c r="B26" s="9">
+        <v>22050119</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="15">
+        <v>38034</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="11">
+        <v>22050123</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="15">
+        <v>38074</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1651,7 +2154,7 @@
   <customSheetViews>
     <customSheetView guid="{28BA9D73-0BB9-4D5C-8BA3-7B9504A74BD3}" filter="1" showAutoFilter="1">
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-      <autoFilter ref="A1:Z125" xr:uid="{1DAE5288-9276-4182-9DE2-CB6130D5E486}"/>
+      <autoFilter ref="A1:Z125" xr:uid="{294ADEFE-FECF-48B6-9030-5A4FC89C06A1}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2128611869"/>
@@ -1667,12 +2170,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A21:A1000"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="43.109375" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/DB_demo/Import Tài Khoản.xlsx
+++ b/DB_demo/Import Tài Khoản.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\cms\DB_demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37769DEC-EC98-489A-8683-0C25F2CF840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDE5A07-265E-415D-9DF1-234829739DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="88">
   <si>
     <t>STT</t>
   </si>
@@ -228,6 +228,87 @@
   </si>
   <si>
     <t>22050123@student.bdu.edu.vn</t>
+  </si>
+  <si>
+    <t>01/10/2004</t>
+  </si>
+  <si>
+    <t>23/10/2004</t>
+  </si>
+  <si>
+    <t>23/08/2004</t>
+  </si>
+  <si>
+    <t>14/06/2004</t>
+  </si>
+  <si>
+    <t>30/06/2003</t>
+  </si>
+  <si>
+    <t>20/11/2004</t>
+  </si>
+  <si>
+    <t>08/01/2002</t>
+  </si>
+  <si>
+    <t>09/09/2004</t>
+  </si>
+  <si>
+    <t>18/09/2004</t>
+  </si>
+  <si>
+    <t>31/08/2004</t>
+  </si>
+  <si>
+    <t>02/01/2004</t>
+  </si>
+  <si>
+    <t>07/03/2004</t>
+  </si>
+  <si>
+    <t>17/09/2004</t>
+  </si>
+  <si>
+    <t>24/10/2004</t>
+  </si>
+  <si>
+    <t>11/04/2004</t>
+  </si>
+  <si>
+    <t>22/02/2004</t>
+  </si>
+  <si>
+    <t>14/03/2004</t>
+  </si>
+  <si>
+    <t>20/04/2004</t>
+  </si>
+  <si>
+    <t>27/03/2004</t>
+  </si>
+  <si>
+    <t>01/01/2004</t>
+  </si>
+  <si>
+    <t>29/05/2004</t>
+  </si>
+  <si>
+    <t>10/08/2003</t>
+  </si>
+  <si>
+    <t>17/04/2004</t>
+  </si>
+  <si>
+    <t>06/07/2004</t>
+  </si>
+  <si>
+    <t>17/02/2004</t>
+  </si>
+  <si>
+    <t>28/03/2004</t>
+  </si>
+  <si>
+    <t>26TH01</t>
   </si>
 </sst>
 </file>
@@ -410,7 +491,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -674,11 +755,11 @@
       <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15">
-        <v>38261</v>
+      <c r="D2" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>35</v>
@@ -698,8 +779,8 @@
       <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="15">
-        <v>38283</v>
+      <c r="D3" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>1</v>
@@ -722,8 +803,8 @@
       <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="15">
-        <v>38222</v>
+      <c r="D4" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>1</v>
@@ -746,8 +827,8 @@
       <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="15">
-        <v>38152</v>
+      <c r="D5" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>1</v>
@@ -770,8 +851,8 @@
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="15">
-        <v>37802</v>
+      <c r="D6" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>1</v>
@@ -794,8 +875,8 @@
       <c r="C7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15">
-        <v>38311</v>
+      <c r="D7" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>1</v>
@@ -818,8 +899,8 @@
       <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="15">
-        <v>37264</v>
+      <c r="D8" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>1</v>
@@ -842,8 +923,8 @@
       <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="15">
-        <v>38239</v>
+      <c r="D9" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>1</v>
@@ -866,8 +947,8 @@
       <c r="C10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="15">
-        <v>38248</v>
+      <c r="D10" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>1</v>
@@ -890,8 +971,8 @@
       <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="15">
-        <v>38230</v>
+      <c r="D11" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>1</v>
@@ -914,8 +995,8 @@
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="15">
-        <v>37988</v>
+      <c r="D12" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>1</v>
@@ -938,8 +1019,8 @@
       <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="15">
-        <v>38053</v>
+      <c r="D13" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>1</v>
@@ -962,8 +1043,8 @@
       <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="15">
-        <v>38247</v>
+      <c r="D14" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>1</v>
@@ -986,8 +1067,8 @@
       <c r="C15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="15">
-        <v>38284</v>
+      <c r="D15" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>1</v>
@@ -1010,8 +1091,8 @@
       <c r="C16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="15">
-        <v>38088</v>
+      <c r="D16" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>1</v>
@@ -1034,8 +1115,8 @@
       <c r="C17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="15">
-        <v>38039</v>
+      <c r="D17" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>1</v>
@@ -1058,8 +1139,8 @@
       <c r="C18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="15">
-        <v>38060</v>
+      <c r="D18" s="15" t="s">
+        <v>77</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>1</v>
@@ -1082,8 +1163,8 @@
       <c r="C19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="15">
-        <v>38097</v>
+      <c r="D19" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>1</v>
@@ -1106,8 +1187,8 @@
       <c r="C20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="15">
-        <v>38073</v>
+      <c r="D20" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>1</v>
@@ -1130,8 +1211,8 @@
       <c r="C21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="15">
-        <v>37987</v>
+      <c r="D21" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>1</v>
@@ -1154,8 +1235,8 @@
       <c r="C22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="15">
-        <v>38136</v>
+      <c r="D22" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>1</v>
@@ -1178,8 +1259,8 @@
       <c r="C23" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="15">
-        <v>37843</v>
+      <c r="D23" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>1</v>
@@ -1202,8 +1283,8 @@
       <c r="C24" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="15">
-        <v>38094</v>
+      <c r="D24" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>1</v>
@@ -1226,8 +1307,8 @@
       <c r="C25" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="15">
-        <v>38174</v>
+      <c r="D25" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>1</v>
@@ -1250,8 +1331,8 @@
       <c r="C26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="15">
-        <v>38034</v>
+      <c r="D26" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>1</v>
@@ -1274,8 +1355,8 @@
       <c r="C27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="15">
-        <v>38074</v>
+      <c r="D27" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>1</v>
@@ -2154,7 +2235,7 @@
   <customSheetViews>
     <customSheetView guid="{28BA9D73-0BB9-4D5C-8BA3-7B9504A74BD3}" filter="1" showAutoFilter="1">
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-      <autoFilter ref="A1:Z125" xr:uid="{294ADEFE-FECF-48B6-9030-5A4FC89C06A1}"/>
+      <autoFilter ref="A1:Z125" xr:uid="{B845B0C7-1F77-4F12-B29E-6570DB2C5875}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2128611869"/>
